--- a/output/CodeSystem-PDexPayerAdjudicationStatus.xlsx
+++ b/output/CodeSystem-PDexPayerAdjudicationStatus.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.1</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-17T14:48:28-05:00</t>
+    <t>2026-03-17T22:49:33-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/CodeSystem-PDexPayerAdjudicationStatus.xlsx
+++ b/output/CodeSystem-PDexPayerAdjudicationStatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T22:49:33-04:00</t>
+    <t>2026-03-19T09:51:30-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/CodeSystem-PDexPayerAdjudicationStatus.xlsx
+++ b/output/CodeSystem-PDexPayerAdjudicationStatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T09:51:30-04:00</t>
+    <t>2026-03-31T21:00:10-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/CodeSystem-PDexPayerAdjudicationStatus.xlsx
+++ b/output/CodeSystem-PDexPayerAdjudicationStatus.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T21:00:10-04:00</t>
+    <t>2026-05-29T12:37:47-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
